--- a/data/guests_junk.xlsx
+++ b/data/guests_junk.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,10 +461,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>validation_status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>validation_reason</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>name_clean</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reject_reason</t>
         </is>
@@ -489,12 +499,14 @@
           <t>Anne Will - 11.01.2009</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Vizepräsidentin des Deutschen Bundestages</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>contains_junk_phrase_words</t>
         </is>
@@ -519,12 +531,14 @@
           <t>Anne Will - 02.02.2020</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>im Bundestag</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>contains_role_word</t>
         </is>
@@ -549,12 +563,14 @@
           <t>Anne Will - 17.09.2023</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Mitglied des Bundestages</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>contains_role_word</t>
         </is>
@@ -587,12 +603,14 @@
           <t>Anne Will - 21.09.2008</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Journalist</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>contains_role_word</t>
         </is>
@@ -617,12 +635,14 @@
           <t>Anne Will - 31.01.2010</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>„dbb beamtenbund</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>contains_role_word</t>
         </is>
@@ -631,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Expertin für Islam</t>
+          <t>Fachbereich Gesundheit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -639,97 +659,103 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>aU_2KMoS</t>
+          <t>I5TF5_eB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>hart aber fair - 07.10.2009</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Expertin für Islam</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>contains_role_word</t>
+          <t>Anne Will - 08.03.2009</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Fachbereich Gesundheit</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>contains_junk_phrase_words</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Gäste</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Innenminister Nordrhein-Westfalen</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Hinweis zum DatenschutzMit Klick auf "Einverstanden" können Sie diese Seite in sozialen Netzwerken weiterempfehlen. Dabei besteht die Möglichkeit, dass Daten von Ihrem Computer zum jeweiligen Anbieter sowie Daten des Anbieters auf Ihren Computer übertragen werden. Diese Zustimmung wird von Ihnen für 24 Stunden erteilt.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>jqfhqThD</t>
+          <t>qvqZ1pfC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>hart aber fair - 22.08.2022</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>FDP</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>party_or_org_token</t>
+          <t>Caren Miosga - 25.08.24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Gäste</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>contains_junk_phrase_words</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fraktionsvorsitzender; Mitglied des Präsidiums</t>
+          <t>Familie Frauen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Christian Dürr</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Christian Dürr</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>jqfhqThD</t>
+          <t>DAQqc733</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hart aber fair - 22.08.2022</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Fraktionsvorsitzender; Mitglied des Präsidiums</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>contains_role_word</t>
+          <t>hart aber fair - 13.09.2006</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Familie Frauen</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>contains_junk_phrase_words</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Die Linke</t>
+          <t>Expertin für Islam</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -737,42 +763,36 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>jqfhqThD</t>
+          <t>aU_2KMoS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>hart aber fair - 22.08.2022</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Die Linke</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>party_or_org_token</t>
+          <t>hart aber fair - 07.10.2009</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Expertin für Islam</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>contains_role_word</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Direktor des Instituts der deutschen Wirtschaft Köln</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Michael Hüther</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Michael Hüther</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>jqfhqThD</t>
@@ -783,51 +803,63 @@
           <t>hart aber fair - 22.08.2022</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Direktor des Instituts der deutschen Wirtschaft Köln</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>contains_junk_phrase_words</t>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>party_or_org_token</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B’90</t>
+          <t>Fraktionsvorsitzender; Mitglied des Präsidiums</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Christian Dürr</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Christian Dürr</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ox2YsqDq</t>
+          <t>jqfhqThD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>maischberger - 19.03.2024</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>B'90</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>party_or_org_token</t>
+          <t>hart aber fair - 22.08.2022</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Fraktionsvorsitzender; Mitglied des Präsidiums</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>contains_role_word</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grüne</t>
+          <t>Die Linke</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -835,20 +867,22 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ox2YsqDq</t>
+          <t>jqfhqThD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>maischberger - 19.03.2024</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Grüne</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+          <t>hart aber fair - 22.08.2022</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Die Linke</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>party_or_org_token</t>
         </is>
@@ -857,37 +891,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>Direktor des Instituts der deutschen Wirtschaft Köln</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Michael Hüther</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Michael Hüther</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ox2YsqDq</t>
+          <t>jqfhqThD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>maischberger - 19.03.2024</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CSU</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>party_or_org_token</t>
+          <t>hart aber fair - 22.08.2022</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Direktor des Instituts der deutschen Wirtschaft Köln</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>contains_junk_phrase_words</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vincent productions GmbH.</t>
+          <t>B’90</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -903,21 +947,23 @@
           <t>maischberger - 19.03.2024</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Vincent productions GmbH.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>org_pattern_found</t>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>B'90</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>too_short_token</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>seine Frau Liselotte</t>
+          <t>Grüne</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -925,58 +971,54 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NFK4zZ1X</t>
+          <t>ox2YsqDq</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>maischberger - 22.04.2008</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>seine Frau Liselotte</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>contains_junk_phrase_words</t>
+          <t>maischberger - 19.03.2024</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Grüne</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>party_or_org_token</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Bundestagsvizepräsident</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bundestagsvizepräsident</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>pMlMm9w9</t>
+          <t>ox2YsqDq</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>maischberger - 12.10.2022</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>FDP</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+          <t>maischberger - 19.03.2024</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CSU</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>party_or_org_token</t>
         </is>
@@ -985,7 +1027,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bundesfinanzminister</t>
+          <t>Vincent productions GmbH.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -993,58 +1035,54 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>cmojDYvR</t>
+          <t>ox2YsqDq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>maischberger - 12.08.2020</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bundesfinanzminister</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>contains_role_word</t>
+          <t>maischberger - 19.03.2024</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Vincent productions GmbH.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>org_pattern_found</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ehemaliger Bundesinnenminister</t>
+          <t>seine Frau Liselotte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Hazar Abaza</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Hazar Abaza</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>cmojDYvR</t>
+          <t>NFK4zZ1X</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>maischberger - 12.08.2020</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ehemaliger Bundesinnenminister</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+          <t>maischberger - 22.04.2008</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>seine Frau Liselotte</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>contains_junk_phrase_words</t>
         </is>
@@ -1053,45 +1091,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Abiturientin; floh 2015 aus Syrien</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hans Rudolf Wöhrl</t>
+          <t>Bundestagsvizepräsident</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hans Rudolf Wöhrl</t>
+          <t>Bundestagsvizepräsident</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>cmojDYvR</t>
+          <t>pMlMm9w9</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>maischberger - 12.08.2020</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Abiturientin; floh 2015 aus Syrien</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>contains_junk_phrase_words</t>
+          <t>maischberger - 12.10.2022</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>party_or_org_token</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Moderatorin ARD-„Morgenmagazin“</t>
+          <t>Bundesfinanzminister</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1107,12 +1147,14 @@
           <t>maischberger - 12.08.2020</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Moderatorin ARD-„Morgenmagazin"</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Bundesfinanzminister</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>contains_role_word</t>
         </is>
@@ -1121,12 +1163,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unternehmer</t>
+          <t>ehemaliger Bundesinnenminister</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hazar Abaza</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Hazar Abaza</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>cmojDYvR</t>
@@ -1137,51 +1187,63 @@
           <t>maischberger - 12.08.2020</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Unternehmer</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>contains_role_word</t>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ehemaliger Bundesinnenminister</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>contains_junk_phrase_words</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Altersforscher</t>
+          <t>Abiturientin; floh 2015 aus Syrien</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hans Rudolf Wöhrl</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Hans Rudolf Wöhrl</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KKP4lr0S</t>
+          <t>cmojDYvR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>maischberger - 02.02.2010</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Altersforscher</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>contains_role_word</t>
+          <t>maischberger - 12.08.2020</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Abiturientin; floh 2015 aus Syrien</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>contains_junk_phrase_words</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>Moderatorin ARD-„Morgenmagazin“</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1189,29 +1251,31 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FPI41BOT</t>
+          <t>cmojDYvR</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>maischberger - 28.03.2023</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>CSU</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>party_or_org_token</t>
+          <t>maischberger - 12.08.2020</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Moderatorin ARD-„Morgenmagazin"</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>contains_role_word</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Die Linke</t>
+          <t>Unternehmer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1219,29 +1283,31 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FPI41BOT</t>
+          <t>cmojDYvR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>maischberger - 28.03.2023</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Die Linke</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>party_or_org_token</t>
+          <t>maischberger - 12.08.2020</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Unternehmer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>contains_role_word</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vincent productions GmbH.</t>
+          <t>Altersforscher</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1249,67 +1315,63 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FPI41BOT</t>
+          <t>KKP4lr0S</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>maischberger - 28.03.2023</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Vincent productions GmbH.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>org_pattern_found</t>
+          <t>maischberger - 02.02.2010</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Altersforscher</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>contains_role_word</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bundesvorsitzender der Jungen Union</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>JU)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>JU)</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>y_UtLThE</t>
+          <t>FPI41BOT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maybrit Illner - 19.05.2016</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Bundesvorsitzender der Jungen Union</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>contains_role_word</t>
+          <t>maischberger - 28.03.2023</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CSU</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>party_or_org_token</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Autor u. a. „Al-Qaidas deutsche Kämpfer</t>
+          <t>Die Linke</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1317,20 +1379,166 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
+          <t>FPI41BOT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>maischberger - 28.03.2023</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Die Linke</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>party_or_org_token</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Vincent productions GmbH.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FPI41BOT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>maischberger - 28.03.2023</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Vincent productions GmbH.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>org_pattern_found</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Bundesvorsitzender der Jungen Union</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JU)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JU)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>y_UtLThE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Maybrit Illner - 19.05.2016</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Bundesvorsitzender der Jungen Union</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>contains_role_word</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Familie Pinzler</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>hat versucht ein Jahr konsequent CO2 zu vermeiden</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>hat versucht ein Jahr konsequent CO2 zu vermeiden</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>L6ft1_3u</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Maybrit Illner - 23.08.2018</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Familie Pinzler</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>contains_junk_phrase_words</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Autor u. a. „Al-Qaidas deutsche Kämpfer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>lGWMBDxs</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Maybrit Illner - 22.01.2015</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Autor u. a. „Al-Qaidas deutsche Kämpfer</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>contains_role_word</t>
         </is>
